--- a/Hyperscale_Cloud_Workload_Aggregation.xlsx
+++ b/Hyperscale_Cloud_Workload_Aggregation.xlsx
@@ -13,7 +13,9 @@
     <sheet name="AI Token Consumption" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Monetization by Workload" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Regional Breakdown" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Methodology &amp; Sources" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Growth — Trad. vs AI" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Margins by Workload &amp; Vendor" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Methodology &amp; Sources" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -120,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -164,6 +166,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -436,6 +444,134 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Q4 2025 Revenue by Provider: Traditional vs AI ($B)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Growth — Trad. vs AI'!D5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="4472C4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Growth — Trad. vs AI'!$A$6:$A$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Growth — Trad. vs AI'!$D$6:$D$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Growth — Trad. vs AI'!F5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="ED7D31"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Growth — Trad. vs AI'!$A$6:$A$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Growth — Trad. vs AI'!$F$6:$F$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Revenue ($B)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -473,6 +609,33 @@
       <rowOff>0</rowOff>
     </from>
     <ext cx="10080000" cy="5040000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="5040000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -4560,16 +4723,2545 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="0000B050"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="42" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="42" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Hyperscaler Cloud Growth — Traditional Workloads vs AI Workloads</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sources: Provider earnings (Q4 2025 / FY26 Q1-Q2), CRN, analyst estimates | Traditional = compute, storage, databases, networking, SaaS; AI = GPU compute, model APIs, ML platforms, AI services</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>A. Revenue Growth Split: Traditional Cloud vs AI Workloads by Provider</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Provider</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Total Cloud Revenue Q4 2025 ($B)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Total YoY Growth</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Traditional Cloud Revenue ($B)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Traditional YoY Growth</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>AI Workload Revenue ($B)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>AI YoY Growth</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>AI as % of Total Revenue</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>AI Contribution to Growth (pp)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Traditional Contribution to Growth (pp)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>2026E Total Growth</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>2026E AI Growth</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>2026E Traditional Growth</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="I6" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>26-28%</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>90-100%</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>15-18%</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>Custom silicon ($10B+ ARR, triple-digit growth); Bedrock multi-billion ARR; traditional reaccelerating on migration wave</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Microsoft Azure</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="J7" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>35-38%</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>70-80%</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>13-17%</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>AI contributes ~22-26pp of Azure's 39% growth (CFO Amy Hood); traditional at 13-17%; deliberately constraining 3P for 1P AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Google Cloud</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>40-45%</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>100-120%</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>22-26%</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>Fastest overall growth; Gemini processing 10B+ tokens/min; $240B backlog; traditional also strong (core infra migration)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Oracle Cloud (OCI)</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>80-100%</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>10-12%</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>OCI IaaS up 68% (AI-driven); SaaS at 11%; $523B RPO backlog (438% YoY); multi-cloud OCI for Meta/NVIDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Alibaba Cloud</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>30-35%</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>100%+</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>10-15%</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>AI product revenue triple-digit growth for 9 consecutive quarters; RMB120B capex over 4 quarters; Qwen models driving adoption</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Huawei Cloud</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>20-25%</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>60-80%</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>10-15%</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>Ascend AI chip ecosystem; 40% CAGR in APAC over 5 years; partner revenue +50%; total Huawei growth cooled to 2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Tencent Cloud</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>18-22%</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>50-60%</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>8-10%</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>FinTech &amp; Business Services segment +10%; HunYuan foundation model; AI-powered ad targeting driving indirect cloud growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>IBM Cloud</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>5-8%</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>30-40%</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>3-5%</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>Hybrid cloud focus (Red Hat); watsonx AI platform; smaller scale vs hyperscalers; enterprise consulting led</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>B. Quarterly Revenue Growth Trajectory (YoY %) — Total, Traditional, and AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Provider</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Q1 2024</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Q2 2024</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Q3 2024</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Q4 2024</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Q2 2025</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Q3 2025</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Trend Direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Total Growth</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E18" s="19" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="I18" s="19" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J18" s="19" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Accelerating</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Traditional Growth</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D19" s="20" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E19" s="20" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F19" s="20" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G19" s="20" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H19" s="20" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I19" s="20" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="J19" s="20" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>AI Growth</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F20" s="19" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H20" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J20" s="19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>Accelerating</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Azure</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Total Growth</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D21" s="20" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E21" s="20" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F21" s="20" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="G21" s="20" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H21" s="20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I21" s="20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J21" s="20" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Plateau ~39-40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Azure</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Traditional Growth</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E22" s="19" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F22" s="19" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G22" s="19" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H22" s="19" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I22" s="19" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="J22" s="19" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Gradual deceleration</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Azure</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>AI Growth</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D23" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E23" s="20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F23" s="20" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G23" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H23" s="20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I23" s="20" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J23" s="20" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>Maturing from high base</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Google Cloud</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Total Growth</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D24" s="19" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E24" s="19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F24" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G24" s="19" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H24" s="19" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="I24" s="19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J24" s="19" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>Sharp acceleration</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Google Cloud</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Traditional Growth</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D25" s="20" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E25" s="20" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F25" s="20" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G25" s="20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H25" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I25" s="20" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J25" s="20" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>Steady improvement</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Google Cloud</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>AI Growth</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D26" s="19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E26" s="19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F26" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I26" s="19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J26" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Surging (Gemini effect)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Oracle OCI</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Total Growth</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D27" s="20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E27" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F27" s="20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G27" s="20" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H27" s="20" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I27" s="20" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J27" s="20" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>Strong acceleration</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Oracle OCI</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Traditional Growth</t>
+        </is>
+      </c>
+      <c r="C28" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D28" s="19" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E28" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F28" s="19" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G28" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H28" s="19" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I28" s="19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J28" s="19" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Oracle OCI</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>AI Growth</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D29" s="20" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E29" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F29" s="20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G29" s="20" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H29" s="20" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I29" s="20" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J29" s="20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>Accelerating sharply</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Alibaba Cloud</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Total Growth</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D30" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E30" s="19" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F30" s="19" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G30" s="19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H30" s="19" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I30" s="19" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="J30" s="19" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Rapid acceleration</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Alibaba Cloud</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Traditional Growth</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D31" s="20" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E31" s="20" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F31" s="20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G31" s="20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H31" s="20" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I31" s="20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J31" s="20" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>Recovering</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Alibaba Cloud</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>AI Growth</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H32" s="19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I32" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>Triple-digit sustained</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FF6600"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Operating &amp; Gross Margins by Workload Type Across Hyperscale Cloud Vendors</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sources: Provider earnings, Wall Street analyst estimates, industry benchmarks | Margins are estimated ranges; providers do not fully disclose per-workload profitability</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>A. Cloud Segment Operating Margins by Provider — Quarterly Trend</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Provider</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Segment Reported</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Q1 2024 Op. Margin</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Q2 2024 Op. Margin</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Q3 2024 Op. Margin</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Q4 2024 Op. Margin</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Q1 2025 Op. Margin</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Q2 2025 Op. Margin</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Q3 2025 Op. Margin</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Q4 2025 Op. Margin</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Trend / Commentary</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Amazon Web Services</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>Ranged 33-40%; Q2 2025 dip from GPU depreciation charge; strong recovery in H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Intelligent Cloud</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Gradual compression from AI infra scaling (CFO: GM% down from AI capex); op income still growing 27% YoY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Google Cloud</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Google Cloud</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Dramatic expansion from near-zero in 2023 to ~30%; fastest margin improvement among top 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Cloud (IaaS + SaaS)</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Steady expansion; non-GAAP op margin ~42%; targeting 30-40% gross margin on AI datacenters over contract life</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Alibaba</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Cloud Intelligence Group</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I10" s="8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>Low single-digit margins; investing heavily in AI infra (RMB120B over 4Q); margin temporarily sacrificed for growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Cloud Business Unit (est.)</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Limited disclosure; estimated thin margins amid heavy R&amp;D (20%+ of revenue); US sanctions constrain chip access</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Tencent</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>FinTech &amp; Biz Services (incl. Cloud)</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>Blended with FinTech; overall segment stable ~37-38%; cloud-only margin likely lower (est. 15-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Software + Infra (incl. Cloud)</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>Hybrid cloud (Red Hat) drives higher-margin software; pure IaaS is lower margin; overall stable ~24-25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>B. Estimated Gross Margins by Workload Type &amp; Vendor</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Note: Providers do not disclose per-workload margins. Estimates are based on analyst reports, industry benchmarks, and workload economics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Workload Type</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Industry Avg Gross Margin</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Azure</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Google Cloud</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Oracle Cloud</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Alibaba Cloud</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Margin Drivers</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Traditional Compute (VMs)</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>65-75%</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>68-73%</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>60-68%</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>55-65%</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Mature, commoditized; custom silicon (Graviton, Ampere) lifts AWS/Azure margins; scale-driven</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Storage (Object / Block)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>75-85%</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>80-85%</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>78-83%</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>75-80%</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>72-78%</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>High margin — low incremental cost per TB at scale; egress premiums add margin; sticky workloads</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Managed Databases</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>70-80%</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>75-80%</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>73-78%</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>72-77%</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>75-82%</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>65-72%</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>High value-add over self-managed; Oracle premium from Autonomous DB; serverless tiers improve margins</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Networking &amp; CDN</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>78-88%</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>82-88%</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>80-85%</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>78-83%</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>75-80%</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>72-78%</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>Egress fees are high margin; CDN capital-intensive but profitable at scale; lock-in effect strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Analytics &amp; Data Warehousing</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>70-80%</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>72-78%</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>73-78%</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>78-83%</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>65-72%</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Query-based pricing (BigQuery) highly profitable; GCP strong with BigQuery; proprietary formats increase switching cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Containers &amp; Serverless</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>65-75%</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>68-75%</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>67-73%</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>68-74%</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>60-68%</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>58-65%</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Control-plane fees add margin; compute underlying is commodity; managed K8s commands premium vs self-hosted</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Security &amp; Identity</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>75-85%</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>78-85%</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>80-86%</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>76-82%</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>72-78%</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>68-74%</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>High margin — software-defined; bundled with compliance requirements; low COGS after initial dev</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>DevOps &amp; CI/CD</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>70-80%</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>72-78%</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>75-82%</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>70-76%</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>65-72%</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>60-68%</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Pipeline-minute pricing; GitHub Actions/Azure DevOps high margin; artifact storage adds recurring revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>AI/ML — GPU Compute (Training)</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>45-55%</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>48-55%</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>45-52%</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>50-58%</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>42-50%</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>40-48%</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Capital-intensive (NVIDIA GPUs expensive); custom silicon (Trainium, TPU) improves margins 10-15pp; depreciation pressure</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>AI/ML — GPU Compute (Inference)</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>50-60%</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>52-60%</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>50-58%</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>55-62%</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>45-55%</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>42-52%</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>Lower power per query than training; optimized chips (Inferentia, TPU v5e) lift margins; demand far exceeds supply</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>AI/ML — Model API (Token-based)</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>55-65%</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>58-65%</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>60-68%</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>58-65%</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>50-58%</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>48-55%</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Software-layer margin on top of GPU; Azure OpenAI premium pricing; token price decline offset by volume surge</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>AI/ML — ML Platform &amp; MLOps</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>60-70%</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>62-70%</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>63-70%</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>60-68%</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>55-63%</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>50-60%</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>SageMaker/Azure ML/Vertex — platform fees; high margin on orchestration layer; compute billed separately</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>AI/ML — Custom Silicon</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>55-70%</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>60-70%</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>55-62%</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>62-72%</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>40-50%</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>AWS Trainium/Inferentia, Google TPU, Azure Maia; higher margin vs NVIDIA due to no GPU vendor margin layer</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>SaaS / Business Apps</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>70-82%</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>75-82%</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>72-78%</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>72-80%</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>65-72%</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Subscription-based; high margin after initial dev; Oracle Fusion/NetSuite strong; Microsoft Dynamics premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>C. AI vs Traditional Cloud — Margin Comparison Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Avg Gross Margin</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Avg Operating Margin</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Capital Intensity</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Margin Trend (2024→2026)</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Key Risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Traditional Cloud (Compute, Storage, DB, Net)</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>70-85%</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>30-45%</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Moderate (declining per unit)</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Stable to slightly expanding</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Commoditization; price competition from smaller providers</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>AI — Training Workloads</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>45-55%</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>15-25%</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Very High (GPU clusters, liquid cooling)</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Compressing near-term; improving long-term with custom silicon</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>GPU depreciation ($2.2B AWS charge); NVIDIA pricing power; rapid obsolescence</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>AI — Inference Workloads</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>50-62%</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>20-30%</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>High (but lower than training)</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Expanding as optimization improves</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Token price collapse (50x/yr median decline); volume must outpace price erosion</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>AI — Model APIs &amp; Platform</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>55-70%</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>25-40%</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Low-Moderate (software layer on GPU infra)</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Expanding as platforms mature</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Commoditization risk from open-source (Llama, DeepSeek); competition drives price to cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>AI — Custom Silicon (TPU, Trainium)</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>55-72%</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>30-45%</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Very High (upfront R&amp;D + fab)</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Expanding rapidly (eliminating NVIDIA margin layer)</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>Execution risk; compatibility with CUDA ecosystem; R&amp;D amortization</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4693,12 +7385,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>AWS Q4 2025 Earnings</t>
+          <t>AWS Q4 2025 Earnings (Feb 2026)</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Revenue: $35.6B; growth: 24% YoY; operating income: $12.5B</t>
+          <t>Revenue: $35.6B; growth: 24%; op income: $12.5B; custom silicon &gt;$10B ARR</t>
         </is>
       </c>
     </row>
@@ -4708,12 +7400,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Microsoft FY26 Q2 Results</t>
+          <t>Microsoft FY26 Q2 Results (Jan 2026)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Intelligent Cloud: $32.9B; Azure growth: 39% YoY</t>
+          <t>Intelligent Cloud: $32.9B; Azure growth: 39%; AI contributes 22-26pp of Azure growth (CFO Amy Hood)</t>
         </is>
       </c>
     </row>
@@ -4723,12 +7415,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Google Q4 2025 Earnings</t>
+          <t>Google Q4 2025 Earnings (Feb 2026)</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Google Cloud: $17.7B; growth: 48% YoY</t>
+          <t>Google Cloud: $17.7B; growth: 48%; op margin ~30%; Gemini 10B+ tokens/min</t>
         </is>
       </c>
     </row>
@@ -4738,12 +7430,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Oracle FY25 Q4 Results</t>
+          <t>Oracle FY26 Q2 Results (Dec 2025)</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Cloud revenue: $6.7B; OCI growth: 52% YoY</t>
+          <t>Cloud revenue: $8.0B; OCI +68%; RPO $523B; targeting 30-40% AI DC gross margin</t>
         </is>
       </c>
     </row>
@@ -4753,12 +7445,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Alibaba Group Quarterly</t>
+          <t>Alibaba Group Quarterly (Nov 2025)</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Cloud revenue growth: 34% YoY; FY2025 ~$11.6B</t>
+          <t>Cloud revenue +34%; AI triple-digit growth 9 consecutive quarters; RMB120B capex</t>
         </is>
       </c>
     </row>
@@ -4768,12 +7460,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Omdia / Informa Tech</t>
+          <t>Huawei Annual Report 2025</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Cloud marketplace forecast ($163B by 2030); workload category projections</t>
+          <t>Total revenue &gt;$122B; cloud partner biz +50%; Ascend AI chip ecosystem</t>
         </is>
       </c>
     </row>
@@ -4783,12 +7475,12 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>McKinsey (2025)</t>
+          <t>Tencent Q3 2025 Results</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>AI workload bifurcation (training vs inference); power density trends</t>
+          <t>FinTech &amp; Biz Services +10%; HunYuan model; overall op margin 38%</t>
         </is>
       </c>
     </row>
@@ -4798,12 +7490,12 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Deloitte Insights</t>
+          <t>Omdia / Informa Tech</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>AI token spend dynamics; enterprise AI cost patterns</t>
+          <t>Cloud marketplace forecast ($163B by 2030); workload category projections</t>
         </is>
       </c>
     </row>
@@ -4813,12 +7505,12 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>ByteIota / WifiTalents</t>
+          <t>McKinsey (2025)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>AI inference cost projections (55% of cloud by 2026); inference chip market</t>
+          <t>AI workload bifurcation (training vs inference); power density trends</t>
         </is>
       </c>
     </row>
@@ -4828,12 +7520,12 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>TLDL / DevTk / BuildMVPFast</t>
+          <t>Deloitte Insights</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>LLM API pricing tables (Feb 2026); model-level token costs</t>
+          <t>AI token spend dynamics; enterprise AI cost patterns</t>
         </is>
       </c>
     </row>
@@ -4843,61 +7535,135 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
+          <t>ByteIota / WifiTalents</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>AI inference cost projections (55% of cloud by 2026); inference chip market</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>TLDL / DevTk / BuildMVPFast</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>LLM API pricing tables (Feb 2026); model-level token costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
           <t>IDC Workload Forecast (2025-2029)</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Public cloud workload trends; IaaS/PaaS workload categorization (19 types)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Wall Street Horizon / Tanay J / LongYield</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>AI gross margin analysis (50-60% AI vs 77%+ traditional); GPU depreciation impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>AInvest / FourWeekMBA / Futurum</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Azure AI growth decomposition; cloud segment margin trends; capex projections</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Methodology Notes</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="19" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>1. Revenue breakdowns by workload category are estimates synthesized from provider earnings, analyst reports, and market sizing data.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="19" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>2. Where exact figures are unavailable, proportional estimates are derived from provider disclosures and third-party research.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="19" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>3. AI token consumption averages are based on published enterprise usage patterns, API rate limits, and cost benchmarks.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="19" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>4. Regional market sizes are estimated from Gartner global totals using regional share data from Synergy and IDC.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="19" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>5. All monetary values are in USD. Growth rates are year-over-year unless otherwise stated.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>6. Data reflects Q4 2025 actuals and early 2026 pricing/forecasts as of February 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>7. Per-workload margins are analyst estimates — providers do not disclose workload-level profitability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>8. AI growth contribution in percentage points derived from Microsoft CFO disclosure (22-26pp) and modeled for other providers.</t>
         </is>
       </c>
     </row>
